--- a/Energiehubs_Uniform_Fases.xlsx
+++ b/Energiehubs_Uniform_Fases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rick Wolbertus\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icthva-my.sharepoint.com/personal/r_wolbertus_hva_nl/Documents/App Energiehub database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A8AEBA-EA9F-4948-B257-42A3EDA8CA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{E6A8AEBA-EA9F-4948-B257-42A3EDA8CA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96A3F478-324D-4F5C-9D2D-1318F0EA8BA3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3046" uniqueCount="1290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3054" uniqueCount="1294">
   <si>
     <t>Project naam:</t>
   </si>
@@ -3890,13 +3890,25 @@
   </si>
   <si>
     <t>Elektriciteit, Warmte, Waterstof</t>
+  </si>
+  <si>
+    <t>Energie Collectief Horsterparc Trekkersveld</t>
+  </si>
+  <si>
+    <t>https://echt.energy/</t>
+  </si>
+  <si>
+    <t>3899 BN Zeewolde</t>
+  </si>
+  <si>
+    <t>52.35148868784078, 5.498718542328413</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3917,6 +3929,12 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF111111"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -3959,12 +3977,13 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4270,7 +4289,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M364"/>
+  <dimension ref="A1:M365"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -13332,49 +13351,49 @@
       </c>
     </row>
     <row r="337" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A337" t="s">
-        <v>344</v>
+      <c r="A337" s="3" t="s">
+        <v>1290</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>544</v>
+        <v>1291</v>
       </c>
       <c r="C337" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D337" t="s">
-        <v>631</v>
+        <v>741</v>
+      </c>
+      <c r="E337" t="s">
+        <v>1292</v>
       </c>
       <c r="F337" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="G337" t="s">
-        <v>1120</v>
+        <v>1293</v>
       </c>
       <c r="H337" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="338" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C338" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D338" t="s">
-        <v>739</v>
-      </c>
-      <c r="E338" t="s">
-        <v>886</v>
+        <v>631</v>
       </c>
       <c r="F338" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="G338" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H338" t="s">
         <v>1134</v>
@@ -13382,22 +13401,25 @@
     </row>
     <row r="339" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C339" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="D339" t="s">
-        <v>633</v>
+        <v>739</v>
+      </c>
+      <c r="E339" t="s">
+        <v>886</v>
       </c>
       <c r="F339" t="s">
         <v>904</v>
       </c>
       <c r="G339" t="s">
-        <v>982</v>
+        <v>1121</v>
       </c>
       <c r="H339" t="s">
         <v>1134</v>
@@ -13405,22 +13427,22 @@
     </row>
     <row r="340" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C340" t="s">
         <v>571</v>
       </c>
       <c r="D340" t="s">
-        <v>740</v>
+        <v>633</v>
       </c>
       <c r="F340" t="s">
         <v>904</v>
       </c>
       <c r="G340" t="s">
-        <v>1122</v>
+        <v>982</v>
       </c>
       <c r="H340" t="s">
         <v>1134</v>
@@ -13428,22 +13450,22 @@
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C341" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D341" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F341" t="s">
         <v>904</v>
       </c>
       <c r="G341" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H341" t="s">
         <v>1134</v>
@@ -13451,36 +13473,30 @@
     </row>
     <row r="342" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C342" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="D342" t="s">
-        <v>742</v>
-      </c>
-      <c r="E342" t="s">
-        <v>887</v>
+        <v>741</v>
       </c>
       <c r="F342" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="G342" t="s">
-        <v>1012</v>
+        <v>1123</v>
       </c>
       <c r="H342" t="s">
         <v>1134</v>
       </c>
-      <c r="I342" t="s">
-        <v>1195</v>
-      </c>
     </row>
     <row r="343" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>549</v>
@@ -13492,10 +13508,10 @@
         <v>742</v>
       </c>
       <c r="E343" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="F343" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="G343" t="s">
         <v>1012</v>
@@ -13504,155 +13520,152 @@
         <v>1134</v>
       </c>
       <c r="I343" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C344" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D344" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E344" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F344" t="s">
         <v>907</v>
       </c>
       <c r="G344" t="s">
-        <v>1124</v>
+        <v>1012</v>
       </c>
       <c r="H344" t="s">
         <v>1134</v>
       </c>
       <c r="I344" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="345" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C345" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D345" t="s">
-        <v>682</v>
+        <v>743</v>
       </c>
       <c r="E345" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="F345" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="G345" t="s">
-        <v>1030</v>
+        <v>1124</v>
       </c>
       <c r="H345" t="s">
         <v>1134</v>
       </c>
       <c r="I345" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="346" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>469</v>
+        <v>551</v>
       </c>
       <c r="C346" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="D346" t="s">
-        <v>744</v>
+        <v>682</v>
       </c>
       <c r="E346" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F346" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="G346" t="s">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="H346" t="s">
         <v>1134</v>
       </c>
       <c r="I346" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="347" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>552</v>
+        <v>469</v>
       </c>
       <c r="C347" t="s">
         <v>571</v>
       </c>
       <c r="D347" t="s">
-        <v>632</v>
+        <v>744</v>
       </c>
       <c r="E347" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="F347" t="s">
         <v>907</v>
       </c>
       <c r="G347" t="s">
-        <v>981</v>
+        <v>1020</v>
       </c>
       <c r="H347" t="s">
         <v>1134</v>
       </c>
       <c r="I347" t="s">
-        <v>1200</v>
-      </c>
-      <c r="L347" t="s">
-        <v>1286</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C348" t="s">
         <v>571</v>
       </c>
       <c r="D348" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E348" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F348" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="G348" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H348" t="s">
         <v>1134</v>
       </c>
       <c r="I348" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="L348" t="s">
         <v>1286</v>
@@ -13660,36 +13673,39 @@
     </row>
     <row r="349" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C349" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="D349" t="s">
-        <v>745</v>
+        <v>633</v>
       </c>
       <c r="E349" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="F349" t="s">
         <v>908</v>
       </c>
       <c r="G349" t="s">
-        <v>1125</v>
+        <v>982</v>
       </c>
       <c r="H349" t="s">
         <v>1134</v>
       </c>
       <c r="I349" t="s">
-        <v>1202</v>
+        <v>1201</v>
+      </c>
+      <c r="L349" t="s">
+        <v>1286</v>
       </c>
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>554</v>
@@ -13698,16 +13714,16 @@
         <v>564</v>
       </c>
       <c r="D350" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E350" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F350" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="G350" t="s">
-        <v>1067</v>
+        <v>1125</v>
       </c>
       <c r="H350" t="s">
         <v>1134</v>
@@ -13718,25 +13734,25 @@
     </row>
     <row r="351" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C351" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="D351" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E351" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F351" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="G351" t="s">
-        <v>998</v>
+        <v>1067</v>
       </c>
       <c r="H351" t="s">
         <v>1134</v>
@@ -13747,274 +13763,268 @@
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C352" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="D352" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E352" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="F352" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="G352" t="s">
-        <v>1126</v>
+        <v>998</v>
       </c>
       <c r="H352" t="s">
         <v>1134</v>
       </c>
       <c r="I352" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C353" t="s">
         <v>565</v>
       </c>
       <c r="D353" t="s">
-        <v>640</v>
+        <v>748</v>
       </c>
       <c r="E353" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="F353" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G353" t="s">
-        <v>989</v>
+        <v>1126</v>
       </c>
       <c r="H353" t="s">
         <v>1134</v>
       </c>
       <c r="I353" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="C354" t="s">
         <v>565</v>
       </c>
       <c r="D354" t="s">
-        <v>749</v>
+        <v>640</v>
       </c>
       <c r="E354" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="F354" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="G354" t="s">
-        <v>930</v>
+        <v>989</v>
       </c>
       <c r="H354" t="s">
         <v>1134</v>
       </c>
       <c r="I354" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C355" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D355" t="s">
-        <v>575</v>
+        <v>749</v>
       </c>
       <c r="E355" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F355" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="G355" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="H355" t="s">
         <v>1134</v>
       </c>
       <c r="I355" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="C356" t="s">
         <v>567</v>
       </c>
       <c r="D356" t="s">
-        <v>645</v>
+        <v>575</v>
       </c>
       <c r="E356" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="F356" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="G356" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="H356" t="s">
         <v>1134</v>
       </c>
       <c r="I356" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>398</v>
+        <v>558</v>
       </c>
       <c r="C357" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D357" t="s">
-        <v>750</v>
+        <v>645</v>
       </c>
       <c r="E357" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="F357" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="G357" t="s">
-        <v>1127</v>
+        <v>924</v>
       </c>
       <c r="H357" t="s">
         <v>1134</v>
       </c>
       <c r="I357" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>559</v>
+        <v>398</v>
       </c>
       <c r="C358" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D358" t="s">
-        <v>620</v>
+        <v>750</v>
       </c>
       <c r="E358" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="F358" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="G358" t="s">
-        <v>971</v>
+        <v>1127</v>
       </c>
       <c r="H358" t="s">
         <v>1134</v>
       </c>
       <c r="I358" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="C359" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D359" t="s">
-        <v>751</v>
+        <v>620</v>
       </c>
       <c r="E359" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="F359" t="s">
         <v>908</v>
       </c>
       <c r="G359" t="s">
-        <v>988</v>
+        <v>971</v>
       </c>
       <c r="H359" t="s">
         <v>1134</v>
       </c>
       <c r="I359" t="s">
-        <v>1202</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="C360" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D360" t="s">
-        <v>752</v>
+        <v>751</v>
+      </c>
+      <c r="E360" t="s">
+        <v>903</v>
       </c>
       <c r="F360" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="G360" t="s">
-        <v>1128</v>
+        <v>988</v>
       </c>
       <c r="H360" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="I360" t="s">
-        <v>1208</v>
-      </c>
-      <c r="J360" t="s">
-        <v>1214</v>
-      </c>
-      <c r="K360" t="s">
-        <v>1280</v>
-      </c>
-      <c r="L360" t="s">
-        <v>1284</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>560</v>
@@ -14023,13 +14033,13 @@
         <v>570</v>
       </c>
       <c r="D361" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F361" t="s">
         <v>906</v>
       </c>
       <c r="G361" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H361" t="s">
         <v>1133</v>
@@ -14041,7 +14051,7 @@
         <v>1214</v>
       </c>
       <c r="K361" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="L361" t="s">
         <v>1284</v>
@@ -14049,7 +14059,7 @@
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>560</v>
@@ -14058,13 +14068,13 @@
         <v>570</v>
       </c>
       <c r="D362" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F362" t="s">
         <v>906</v>
       </c>
       <c r="G362" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H362" t="s">
         <v>1133</v>
@@ -14076,7 +14086,7 @@
         <v>1214</v>
       </c>
       <c r="K362" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="L362" t="s">
         <v>1284</v>
@@ -14084,7 +14094,7 @@
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>560</v>
@@ -14093,13 +14103,13 @@
         <v>570</v>
       </c>
       <c r="D363" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F363" t="s">
         <v>906</v>
       </c>
       <c r="G363" t="s">
-        <v>1076</v>
+        <v>1130</v>
       </c>
       <c r="H363" t="s">
         <v>1133</v>
@@ -14108,10 +14118,10 @@
         <v>1208</v>
       </c>
       <c r="J363" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="K363" t="s">
-        <v>1221</v>
+        <v>1280</v>
       </c>
       <c r="L363" t="s">
         <v>1284</v>
@@ -14119,7 +14129,7 @@
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>560</v>
@@ -14128,27 +14138,62 @@
         <v>570</v>
       </c>
       <c r="D364" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F364" t="s">
         <v>906</v>
       </c>
       <c r="G364" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H364" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I364" t="s">
+        <v>1208</v>
+      </c>
+      <c r="J364" t="s">
+        <v>1216</v>
+      </c>
+      <c r="K364" t="s">
+        <v>1221</v>
+      </c>
+      <c r="L364" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="365" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A365" t="s">
+        <v>371</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C365" t="s">
+        <v>570</v>
+      </c>
+      <c r="D365" t="s">
+        <v>756</v>
+      </c>
+      <c r="F365" t="s">
+        <v>906</v>
+      </c>
+      <c r="G365" t="s">
         <v>1130</v>
       </c>
-      <c r="H364" t="s">
+      <c r="H365" t="s">
         <v>1132</v>
       </c>
-      <c r="I364" t="s">
+      <c r="I365" t="s">
         <v>1209</v>
       </c>
-      <c r="J364" t="s">
+      <c r="J365" t="s">
         <v>1214</v>
       </c>
-      <c r="K364" t="s">
+      <c r="K365" t="s">
         <v>1282</v>
       </c>
-      <c r="L364" t="s">
+      <c r="L365" t="s">
         <v>1284</v>
       </c>
     </row>
@@ -14462,34 +14507,34 @@
     <hyperlink ref="B334" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
     <hyperlink ref="B335" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
     <hyperlink ref="B336" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="B337" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="B338" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="B339" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="B340" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="B341" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="B342" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="B343" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="B344" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="B345" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="B346" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="B347" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="B348" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="B349" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="B350" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="B351" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="B352" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="B353" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="B354" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="B355" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="B356" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="B357" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="B358" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="B359" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="B360" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="B361" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="B362" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="B363" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="B364" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="B338" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="B339" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="B340" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="B341" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="B342" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="B343" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="B344" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="B345" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="B346" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="B347" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="B348" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="B349" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="B350" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="B351" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="B352" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="B353" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="B354" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="B355" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="B356" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="B357" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="B358" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="B359" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="B360" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="B361" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="B362" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="B363" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="B364" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="B365" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
